--- a/pensum/ma05/LOM_Ovingsark_Markedsforing_kap05_Kundelonnsomhet_NY.xlsx
+++ b/pensum/ma05/LOM_Ovingsark_Markedsforing_kap05_Kundelonnsomhet_NY.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Hva som er igjen av hver omsatt krone etter materiell og underentreprenører.</t>
+          <t>Hva som er igjen av hver omsatt krone etter materiell og innleide montører.</t>
         </is>
       </c>
     </row>
@@ -1074,11 +1074,11 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>− varekostnad underentreprenør</t>
+          <t>− varekostnad innleide montører</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>3660000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="8">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>9406000</v>
+        <v>12666000</v>
       </c>
     </row>
     <row r="12">
@@ -1263,7 +1263,7 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="E19" s="17">
         <f>B19*$B$5</f>
@@ -1304,7 +1304,7 @@
         <v>0.15</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="E20" s="17">
         <f>B20*$B$5</f>
@@ -1345,7 +1345,7 @@
         <v>0.36</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>0.4220903361344537</v>
+        <v>0.5577836134453779</v>
       </c>
       <c r="E21" s="17">
         <f>B21*$B$5</f>
@@ -1386,7 +1386,7 @@
         <v>0.13</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="E22" s="17">
         <f>B22*$B$5</f>
@@ -1427,7 +1427,7 @@
         <v>0.11</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="E23" s="17">
         <f>B23*$B$5</f>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Omsetning minus materiell og underentreprenører.</t>
+          <t>Omsetning minus materiell og innleide montører.</t>
         </is>
       </c>
     </row>

--- a/pensum/ma05/LOM_Ovingsark_Markedsforing_kap05_Kundelonnsomhet_NY.xlsx
+++ b/pensum/ma05/LOM_Ovingsark_Markedsforing_kap05_Kundelonnsomhet_NY.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">3. Huseierne har høyest dekningsgrad. Hvem gir mest per montørtime av huseierne og borettslagene?</t>
   </si>
   <si>
-    <t xml:space="preserve">Tallene er Nordlys Elektro AS sine for 2026 (sammendraget til kap. 5 og regnearket). Kilde: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5.5, og Økonomistyring for LØM-emnet, kap. 7. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Tallene er Nordlys Elektro AS sine for 2026 (sammendraget til kap. 5 og regnearket). Kilde: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5.7, og Økonomistyring for LØM-emnet, kap. 7. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Kundelønnsomhet per segment</t>
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Arket svarer på ett spørsmål: hvilket segment gir mest igjen per montørtime — og holder svaret når salgsarbeidet og kredittiden regnes med?</t>
   </si>
   <si>
-    <t xml:space="preserve">Merk: montørlønna er IKKE trukket fra dekningsbidraget her. Den er fast på kort sikt og følger montøren, ikke kunden. Det er derfor tallene er høyere enn dekningsbidraget per oppdragstype i Bok 1 kap. 7.</t>
+    <t xml:space="preserve">Merk: montørlønna er IKKE trukket fra dekningsbidraget her. Den er fast på kort sikt og følger montøren, ikke kunden. Det er derfor tallene er høyere enn dekningsbidraget per oppdragstype i Økonomistyring for LØM-emnet kap. 7.</t>
   </si>
   <si>
     <t xml:space="preserve">Tallene som ligger inne er et eksempel fra en elektrobedrift. Bytt dem ut med dine egne — alle formler følger med.</t>
@@ -321,7 +321,7 @@
     <t xml:space="preserve">Kilder</t>
   </si>
   <si>
-    <t xml:space="preserve">Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, 4. utg., kap. 5.1 til 5.8. Knapp faktor og dekningsbidrag: Bok 1 Økonomistyring kap. 2, 7 og 8. Kundefordringer og kapitalbinding: Bok 1 kap. 3 og 4.</t>
+    <t xml:space="preserve">Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, 4. utg., kap. 5.1 til 5.8. Knapp faktor og dekningsbidrag: Økonomistyring for LØM-emnet, kap. 2, 7 og 8. Kundefordringer og kapitalbinding: Økonomistyring for LØM-emnet kap. 3 og 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Salgskostnad og kredittid per segment er ikke lærebokas begreper. De er en utvidelse av lærebokas krav om at et segment skal vurderes på lønnsomhet, og de er merket som det. Læreboka gjelder foran arket.</t>
@@ -508,7 +508,7 @@
     <t xml:space="preserve">Prøv dette: sett dekningsgraden for huseiere ned til nivået i de andre segmentene, og se om rekkefølgen i kolonne H endrer seg. Det gjør den ikke — og det er poenget: prosenten avgjør ikke.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, 4. utg., kap. 5.1 til 5.3 og 5.7 om lønnsomhetspotensial. Knapp faktor: Bok 1 Økonomistyring kap. 7. Tallene er Nordlys Elektro AS sine egne for 2026.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, 4. utg., kap. 5.1 til 5.3 og 5.7 om lønnsomhetspotensial. Knapp faktor: Økonomistyring for LØM-emnet, kap. 7. Tallene er Nordlys Elektro AS sine egne for 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva er igjen når salgsarbeidet og kreditten er betalt?</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">Prøv dette: sett kredittdagene for entreprenørene ned til tretti, og se hvor mye kundelønnsomheten stiger. Det er en forhandling, ikke en prisøkning.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes kap. 5.7 om lønnsomhetspotensial. Salgskostnaden og kredittiden er ikke lærebokas begreper, men en utvidelse: læreboka sier at segmentet må vurderes på lønnsomhet, og dette er hvordan man gjør det i en installasjonsbedrift. Kapitalbindingen henger sammen med kundefordringene i Bok 1 Økonomistyring kap. 3 og 4.</t>
+    <t xml:space="preserve">Kilde: Hjertnes kap. 5.7 om lønnsomhetspotensial. Salgskostnaden og kredittiden er ikke lærebokas begreper, men en utvidelse: læreboka sier at segmentet må vurderes på lønnsomhet, og dette er hvordan man gjør det i en installasjonsbedrift. Kapitalbindingen henger sammen med kundefordringene i Økonomistyring for LØM-emnet, kap. 3 og 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Tre scenarioer</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">Hva som SKAL stå her med tallene som ligger inne</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes kap. 5.7 om segmentets størrelse og lønnsomhetspotensial og kap. 5.8 om målgruppestrategiene. Serviceoppdragets størrelse er Nordlys' egen, fra Bok 1 Økonomistyring kap. 8.</t>
+    <t xml:space="preserve">Kilde: Hjertnes kap. 5.7 om segmentets størrelse og lønnsomhetspotensial og kap. 5.8 om målgruppestrategiene. Serviceoppdragets størrelse er Nordlys' egen, fra Økonomistyring for LØM-emnet, kap. 8.</t>
   </si>
   <si>
     <t xml:space="preserve">Samme regnestykke, tomt. Fem segmenter er nok for de aller fleste.</t>
